--- a/artfynd/A 57581-2024 artfynd.xlsx
+++ b/artfynd/A 57581-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AZ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262489</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262477</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262502</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262547</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262552</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262559</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1447,6 +1482,11 @@
       <c r="AY8" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262565</t>
         </is>
       </c>
     </row>
@@ -1564,6 +1604,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262524</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1675,6 +1720,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262526</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1786,6 +1836,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262540</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1897,6 +1952,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262514</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2008,6 +2068,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262531</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2119,6 +2184,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262551</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2230,6 +2300,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262495</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2341,6 +2416,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262504</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2452,6 +2532,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262513</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2563,6 +2648,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262493</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2674,6 +2764,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262507</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2785,6 +2880,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262509</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2896,6 +2996,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262516</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3007,6 +3112,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262533</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3123,6 +3233,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262563</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3239,6 +3354,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262568</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3371,6 +3491,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262497</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3487,6 +3612,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262483</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3603,6 +3733,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262485</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3719,6 +3854,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262487</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3835,6 +3975,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262491</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3951,6 +4096,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262511</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4067,6 +4217,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262518</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4183,6 +4338,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262520</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4299,6 +4459,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262522</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4415,6 +4580,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262542</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4536,6 +4706,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262544</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4667,6 +4842,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262549</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4783,6 +4963,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262554</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4899,6 +5084,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262566</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5018,6 +5208,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262561</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5129,6 +5324,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262478</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5240,8 +5440,55 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135262529</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 57581-2024 artfynd.xlsx
+++ b/artfynd/A 57581-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135262489</v>
       </c>
       <c r="B2" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135262477</v>
       </c>
       <c r="B3" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135262502</v>
       </c>
       <c r="B4" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135262547</v>
       </c>
       <c r="B5" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135262552</v>
       </c>
       <c r="B6" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135262559</v>
       </c>
       <c r="B7" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135262565</v>
       </c>
       <c r="B8" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135262524</v>
       </c>
       <c r="B9" t="n">
-        <v>80382</v>
+        <v>80420</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>135262526</v>
       </c>
       <c r="B10" t="n">
-        <v>80382</v>
+        <v>80420</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>135262540</v>
       </c>
       <c r="B11" t="n">
-        <v>80382</v>
+        <v>80420</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>135262514</v>
       </c>
       <c r="B12" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>135262531</v>
       </c>
       <c r="B13" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>135262551</v>
       </c>
       <c r="B14" t="n">
-        <v>80492</v>
+        <v>80530</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>135262495</v>
       </c>
       <c r="B15" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>135262504</v>
       </c>
       <c r="B16" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>135262513</v>
       </c>
       <c r="B17" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>135262493</v>
       </c>
       <c r="B18" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>135262507</v>
       </c>
       <c r="B19" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>135262509</v>
       </c>
       <c r="B20" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>135262516</v>
       </c>
       <c r="B21" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>135262533</v>
       </c>
       <c r="B22" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>135262563</v>
       </c>
       <c r="B23" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>135262568</v>
       </c>
       <c r="B24" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>135262497</v>
       </c>
       <c r="B25" t="n">
-        <v>57847</v>
+        <v>57852</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>135262483</v>
       </c>
       <c r="B26" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>135262485</v>
       </c>
       <c r="B27" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>135262487</v>
       </c>
       <c r="B28" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>135262491</v>
       </c>
       <c r="B29" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>135262511</v>
       </c>
       <c r="B30" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>135262518</v>
       </c>
       <c r="B31" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>135262520</v>
       </c>
       <c r="B32" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>135262522</v>
       </c>
       <c r="B33" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>135262542</v>
       </c>
       <c r="B34" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>135262544</v>
       </c>
       <c r="B35" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4717,7 +4717,7 @@
         <v>135262549</v>
       </c>
       <c r="B36" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>135262554</v>
       </c>
       <c r="B37" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>135262566</v>
       </c>
       <c r="B38" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>135262561</v>
       </c>
       <c r="B39" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>135262478</v>
       </c>
       <c r="B40" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5335,7 +5335,7 @@
         <v>135262529</v>
       </c>
       <c r="B41" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 57581-2024 artfynd.xlsx
+++ b/artfynd/A 57581-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135262489</v>
       </c>
       <c r="B2" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135262477</v>
       </c>
       <c r="B3" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135262502</v>
       </c>
       <c r="B4" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135262547</v>
       </c>
       <c r="B5" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135262552</v>
       </c>
       <c r="B6" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135262559</v>
       </c>
       <c r="B7" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135262565</v>
       </c>
       <c r="B8" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135262524</v>
       </c>
       <c r="B9" t="n">
-        <v>80420</v>
+        <v>80447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>135262526</v>
       </c>
       <c r="B10" t="n">
-        <v>80420</v>
+        <v>80447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>135262540</v>
       </c>
       <c r="B11" t="n">
-        <v>80420</v>
+        <v>80447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>135262514</v>
       </c>
       <c r="B12" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>135262531</v>
       </c>
       <c r="B13" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>135262551</v>
       </c>
       <c r="B14" t="n">
-        <v>80530</v>
+        <v>80557</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>135262495</v>
       </c>
       <c r="B15" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         <v>135262504</v>
       </c>
       <c r="B16" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>135262513</v>
       </c>
       <c r="B17" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>135262493</v>
       </c>
       <c r="B18" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>135262507</v>
       </c>
       <c r="B19" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>135262509</v>
       </c>
       <c r="B20" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>135262516</v>
       </c>
       <c r="B21" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         <v>135262533</v>
       </c>
       <c r="B22" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>135262478</v>
       </c>
       <c r="B40" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5335,7 +5335,7 @@
         <v>135262529</v>
       </c>
       <c r="B41" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
